--- a/artfynd/A 30185-2026 artfynd.xlsx
+++ b/artfynd/A 30185-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135633701</v>
       </c>
       <c r="B2" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135633702</v>
       </c>
       <c r="B5" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>135633704</v>
       </c>
       <c r="B6" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>135633706</v>
       </c>
       <c r="B7" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>135633708</v>
       </c>
       <c r="B8" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30185-2026 artfynd.xlsx
+++ b/artfynd/A 30185-2026 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>135633702</v>
       </c>
       <c r="B5" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>135633704</v>
       </c>
       <c r="B6" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>135633706</v>
       </c>
       <c r="B7" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>135633708</v>
       </c>
       <c r="B8" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30185-2026 artfynd.xlsx
+++ b/artfynd/A 30185-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135633701</v>
       </c>
       <c r="B2" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135633700</v>
       </c>
       <c r="B3" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135633703</v>
       </c>
       <c r="B4" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135633702</v>
       </c>
       <c r="B5" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>135633704</v>
       </c>
       <c r="B6" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>135633706</v>
       </c>
       <c r="B7" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>135633708</v>
       </c>
       <c r="B8" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30185-2026 artfynd.xlsx
+++ b/artfynd/A 30185-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135633701</v>
       </c>
       <c r="B2" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135633702</v>
       </c>
       <c r="B5" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>135633704</v>
       </c>
       <c r="B6" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>135633706</v>
       </c>
       <c r="B7" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>135633708</v>
       </c>
       <c r="B8" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30185-2026 artfynd.xlsx
+++ b/artfynd/A 30185-2026 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>135633702</v>
       </c>
       <c r="B5" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>135633704</v>
       </c>
       <c r="B6" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>135633706</v>
       </c>
       <c r="B7" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>135633708</v>
       </c>
       <c r="B8" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30185-2026 artfynd.xlsx
+++ b/artfynd/A 30185-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135633701</v>
       </c>
       <c r="B2" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135633700</v>
       </c>
       <c r="B3" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135633703</v>
       </c>
       <c r="B4" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135633702</v>
       </c>
       <c r="B5" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>135633704</v>
       </c>
       <c r="B6" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>135633706</v>
       </c>
       <c r="B7" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>135633708</v>
       </c>
       <c r="B8" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30185-2026 artfynd.xlsx
+++ b/artfynd/A 30185-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135633701</v>
       </c>
       <c r="B2" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135633700</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>135633703</v>
       </c>
       <c r="B4" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135633702</v>
       </c>
       <c r="B5" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>135633704</v>
       </c>
       <c r="B6" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>135633706</v>
       </c>
       <c r="B7" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>135633708</v>
       </c>
       <c r="B8" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
